--- a/data/trans_orig/P43C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P43C-Habitat-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2007</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2007 (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317649</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292397</t>
+          <t>292982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>341803</t>
+          <t>344052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>317649</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>292397</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>341803</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>43,35%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>363</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>356929</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>330526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>381596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>332775</t>
+          <t>330526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>382181</t>
+          <t>381596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>356929</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>332775</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>382181</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>56,65%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>682</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674578</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674578</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674578</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>674578</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>674578</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>674578</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>495667</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>463808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>525577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>464816</t>
+          <t>463808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>527472</t>
+          <t>525577</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>495667</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>464816</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>527472</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>51,83%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>48,6%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>55,15%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460729</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>430819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428924</t>
+          <t>430819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491580</t>
+          <t>492588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>460729</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>428924</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>491580</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>48,17%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>44,85%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>51,4%</t>
+          <t>51,5%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>897</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>956396</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>956396</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>956396</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>956396</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>956396</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>956396</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>381620</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>354217</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>355794</t>
+          <t>354217</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>404449</t>
+          <t>405337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>381620</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>355794</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>404449</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>56,6%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>59,98%</t>
+          <t>60,11%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292662</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>268945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>320065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269833</t>
+          <t>268945</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318488</t>
+          <t>320065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>292662</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>269833</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>318488</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>43,4%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>40,02%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>674282</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>674282</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>674282</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>595413</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>565122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>629694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>566070</t>
+          <t>565122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>624292</t>
+          <t>629694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>595413</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>566070</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>624292</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>58,27%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>61,1%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>409</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>426381</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>456672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>397502</t>
+          <t>392100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>455724</t>
+          <t>456672</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>426381</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>397502</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>455724</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>41,73%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>44,6%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>981</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1021794</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1021794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1021794</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1021794</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1021794</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1021794</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2095,37 +1615,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1790349</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1732279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1846842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1729293</t>
+          <t>1732279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1845045</t>
+          <t>1846842</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1790349</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1729293</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1845045</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>51,98%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>55,46%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -2208,37 +1693,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1536701</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1480208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1594771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1482005</t>
+          <t>1480208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1597757</t>
+          <t>1594771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1536701</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1482005</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1597757</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>46,19%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>44,54%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>48,02%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -2321,37 +1771,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3327050</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3327050</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3327050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,41 +1835,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3247</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3327050</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3327050</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3327050</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2433,14 +1848,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2454,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2473,25 +1887,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2012</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2012 (tasa de respuesta: 98,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +1909,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2511,17 +1918,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2592,41 +1988,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2649,13 +2010,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2670,37 +2024,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>398</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>431039</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>455070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>405584</t>
+          <t>403092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>457891</t>
+          <t>455070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,47 +2084,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>431039</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>405584</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>457891</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>62,47%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>58,79%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>66,37%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -2783,37 +2102,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>245</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258901</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>286848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232049</t>
+          <t>234870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284356</t>
+          <t>286848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,47 +2162,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>258901</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>232049</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>284356</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>37,53%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>33,63%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>41,21%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -2896,37 +2180,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>643</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689940</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689940</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2960,41 +2244,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>689940</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>689940</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>689940</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3013,37 +2262,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>662081</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>632346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>630143</t>
+          <t>632346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>692443</t>
+          <t>695696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,47 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>662081</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>630143</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>692443</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>64,61%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>61,49%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>67,57%</t>
+          <t>67,89%</t>
         </is>
       </c>
     </row>
@@ -3126,37 +2340,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362725</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>329110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332363</t>
+          <t>329110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>394663</t>
+          <t>392460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,47 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>362725</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>332363</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>394663</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>35,39%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>32,43%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>38,51%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -3239,37 +2418,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>933</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1024806</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1024806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1024806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3303,41 +2482,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1024806</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1024806</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1024806</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3356,37 +2500,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>485</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>539760</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564426</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>510537</t>
+          <t>513818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>564878</t>
+          <t>564426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,47 +2560,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>539760</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>510537</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>564878</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>70,3%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>73,57%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -3469,37 +2578,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>228079</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202961</t>
+          <t>203413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257302</t>
+          <t>254021</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,47 +2638,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>228079</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>202961</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>257302</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>29,7%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>26,43%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -3582,37 +2656,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>697</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>767839</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>767839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>767839</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3646,41 +2720,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>767839</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>767839</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>767839</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3699,37 +2738,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>660096</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>626290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>629143</t>
+          <t>626290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>691169</t>
+          <t>691321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,47 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>660096</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>629143</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>691169</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>60,51%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>66,47%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -3812,37 +2816,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>366</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>379673</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>413479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348600</t>
+          <t>348448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>410626</t>
+          <t>413479</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,47 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>379673</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>348600</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>410626</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>33,53%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>39,49%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -3925,37 +2894,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>991</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1039769</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1039769</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1039769</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3989,41 +2958,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1039769</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1039769</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1039769</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4042,37 +2976,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2292976</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2233561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2345963</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2239652</t>
+          <t>2233561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2357380</t>
+          <t>2345963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,47 +3036,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2292976</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2239652</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2357380</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>63,58%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>66,93%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -4155,37 +3054,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1229377</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1176390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1288792</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1164973</t>
+          <t>1176390</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1282701</t>
+          <t>1288792</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,47 +3114,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1229377</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1164973</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1282701</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>34,9%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -4268,37 +3132,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3522353</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3522353</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3522353</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4332,41 +3196,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3522353</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3522353</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3522353</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4380,14 +3209,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -4401,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4420,25 +3248,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2016</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2016 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +3270,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4458,17 +3279,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -4539,41 +3349,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -4596,13 +3371,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4617,37 +3385,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>369</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370525</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>396955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>343626</t>
+          <t>347554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>396335</t>
+          <t>396955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,47 +3445,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>370525</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>343626</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>396335</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>55,67%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>51,63%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>59,55%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -4730,37 +3463,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>290</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>294992</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>268562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317963</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269182</t>
+          <t>268562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>321891</t>
+          <t>317963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,47 +3523,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>294992</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>269182</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>321891</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>44,33%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>40,45%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>48,37%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3541,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>659</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>665517</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>665517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>665517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4907,41 +3605,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>665517</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>665517</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>665517</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4960,37 +3623,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>631</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>668829</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>639013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>700781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>637955</t>
+          <t>639013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>698073</t>
+          <t>700781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,47 +3683,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>668829</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>637955</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>698073</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>65,15%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>68,0%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -5073,37 +3701,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>331</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>357768</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328524</t>
+          <t>325816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>388642</t>
+          <t>387584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,47 +3761,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>357768</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>328524</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>388642</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>34,85%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>32,0%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>37,86%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -5186,37 +3779,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1026597</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1026597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1026597</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5250,41 +3843,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1026597</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1026597</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1026597</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5303,37 +3861,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506968</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>534238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>476194</t>
+          <t>480647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>532948</t>
+          <t>534238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,47 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>506968</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>476194</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>532948</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>64,93%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>60,99%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>68,26%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -5416,37 +3939,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>252</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273836</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>246566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247856</t>
+          <t>246566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>304610</t>
+          <t>300157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,47 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>273836</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>247856</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>304610</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>35,07%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>31,74%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>39,01%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4017,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>732</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>780804</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>780804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>780804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5593,41 +4081,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>780804</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>780804</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>780804</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5646,37 +4099,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>643</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695903</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>666322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>725740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>663512</t>
+          <t>666322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>728004</t>
+          <t>725740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,47 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>695903</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>663512</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>728004</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>67,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>64,18%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>70,42%</t>
+          <t>70,2%</t>
         </is>
       </c>
     </row>
@@ -5759,37 +4177,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337850</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305749</t>
+          <t>308013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370241</t>
+          <t>367431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,47 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>337850</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>305749</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>370241</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>32,68%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>29,58%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>35,82%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -5872,37 +4255,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>950</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1033753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1033753</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1033753</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5936,41 +4319,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1033753</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1033753</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1033753</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5989,37 +4337,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2242226</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2183875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2297736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2184223</t>
+          <t>2183875</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2299181</t>
+          <t>2297736</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,47 +4397,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2242226</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2184223</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2299181</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>62,29%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -6102,37 +4415,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1264446</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1208936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1322797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1207491</t>
+          <t>1208936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1322449</t>
+          <t>1322797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,47 +4475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1180</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1264446</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1207491</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1322449</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>36,06%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>37,71%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -6215,37 +4493,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3506672</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3506672</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3506672</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6279,41 +4557,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3506672</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3506672</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3506672</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6327,14 +4570,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -6348,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6367,25 +4609,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si alguna vez le han realizado una citología vaginal en 2023</t>
+          <t>Población según si alguna vez le han realizado una citología vaginal en 2023 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +4631,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6405,17 +4640,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -6486,41 +4710,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -6543,13 +4732,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -6564,37 +4746,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267433</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +4791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249040</t>
+          <t>248548</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285916</t>
+          <t>285365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,47 +4806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>267433</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>249040</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>285916</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>49,2%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>56,49%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -6677,37 +4824,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>238729</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +4869,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220246</t>
+          <t>220797</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257122</t>
+          <t>257614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,47 +4884,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>238729</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>220246</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>257122</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>47,16%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>43,51%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>50,8%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -6790,37 +4902,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>933</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506162</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506162</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506162</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6854,41 +4966,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>506162</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>506162</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>506162</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6907,37 +4984,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>643</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380965</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>356534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>404163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +5029,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>357717</t>
+          <t>356534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>402860</t>
+          <t>404163</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,47 +5044,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>380965</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>357717</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>402860</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>52,29%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -7020,37 +5062,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>522</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347532</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>371963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325637</t>
+          <t>324334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370780</t>
+          <t>371963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,47 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>347532</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>325637</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>370780</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>47,71%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>44,7%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -7133,37 +5140,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>728497</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>728497</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>728497</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7197,41 +5204,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>728497</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>728497</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>728497</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7250,37 +5222,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353936</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>508272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +5267,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155619</t>
+          <t>167640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>503517</t>
+          <t>508272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,47 +5282,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>353936</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>155619</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>503517</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>69,49%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -7363,37 +5300,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370603</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216267</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>556899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +5345,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221022</t>
+          <t>216267</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>568920</t>
+          <t>556899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,47 +5360,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>370603</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>221022</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>568920</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -7476,37 +5378,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>726</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724539</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7540,41 +5442,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>724539</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>724539</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>724539</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7593,37 +5460,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>777</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568955</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>530715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>634122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +5505,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>532307</t>
+          <t>530715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>631797</t>
+          <t>634122</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,47 +5520,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>568955</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>532307</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>631797</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>67,08%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>62,75%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>74,48%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -7706,37 +5538,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>279275</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317515</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +5583,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>216433</t>
+          <t>214108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315923</t>
+          <t>317515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,47 +5598,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>279275</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>216433</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>315923</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>32,92%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>25,52%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -7819,37 +5616,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>848230</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>848230</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>848230</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7883,41 +5680,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1164</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>848230</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>848230</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>848230</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7936,37 +5698,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1571289</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1180025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1722853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +5743,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1229447</t>
+          <t>1180025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1725596</t>
+          <t>1722853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,47 +5758,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2420</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1571289</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1229447</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1725596</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>43,79%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>61,47%</t>
+          <t>61,37%</t>
         </is>
       </c>
     </row>
@@ -8049,37 +5776,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1236139</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1084575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1627403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +5821,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1081832</t>
+          <t>1084575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1577981</t>
+          <t>1627403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,47 +5836,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1236139</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1081832</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1577981</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>38,53%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>56,21%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -8162,37 +5854,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2807428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2807428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2807428</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8226,41 +5918,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2807428</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>2807428</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2807428</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8274,14 +5931,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P43C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P43C-Habitat-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>292982</t>
+          <t>292949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344052</t>
+          <t>344812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292982</t>
+          <t>292949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>344052</t>
+          <t>344812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330526</t>
+          <t>329766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381596</t>
+          <t>381629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>330526</t>
+          <t>329766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>381596</t>
+          <t>381629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>463808</t>
+          <t>463803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>525577</t>
+          <t>527455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>463808</t>
+          <t>463803</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>525577</t>
+          <t>527455</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430819</t>
+          <t>428941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492588</t>
+          <t>492593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>430819</t>
+          <t>428941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492588</t>
+          <t>492593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>354217</t>
+          <t>355290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>405337</t>
+          <t>407470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>354217</t>
+          <t>355290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>405337</t>
+          <t>407470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268945</t>
+          <t>266812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320065</t>
+          <t>318992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>268945</t>
+          <t>266812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320065</t>
+          <t>318992</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>565122</t>
+          <t>564533</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>629694</t>
+          <t>627819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>565122</t>
+          <t>564533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>629694</t>
+          <t>627819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>392100</t>
+          <t>393975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>456672</t>
+          <t>457261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>392100</t>
+          <t>393975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>456672</t>
+          <t>457261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1732279</t>
+          <t>1728222</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1846842</t>
+          <t>1846242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1732279</t>
+          <t>1728222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1846842</t>
+          <t>1846242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1480208</t>
+          <t>1480808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1594771</t>
+          <t>1598828</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1480208</t>
+          <t>1480808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1594771</t>
+          <t>1598828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>403092</t>
+          <t>405174</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>455070</t>
+          <t>454472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>403092</t>
+          <t>405174</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>455070</t>
+          <t>454472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234870</t>
+          <t>235468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286848</t>
+          <t>284766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234870</t>
+          <t>235468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286848</t>
+          <t>284766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>632346</t>
+          <t>628600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>695696</t>
+          <t>690321</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>632346</t>
+          <t>628600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>695696</t>
+          <t>690321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329110</t>
+          <t>334485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392460</t>
+          <t>396206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329110</t>
+          <t>334485</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>392460</t>
+          <t>396206</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>513818</t>
+          <t>513537</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>564426</t>
+          <t>566599</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>513818</t>
+          <t>513537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>564426</t>
+          <t>566599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>203413</t>
+          <t>201240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>254021</t>
+          <t>254302</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>203413</t>
+          <t>201240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254021</t>
+          <t>254302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>626290</t>
+          <t>630564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>691321</t>
+          <t>696516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>626290</t>
+          <t>630564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>691321</t>
+          <t>696516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>348448</t>
+          <t>343253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>413479</t>
+          <t>409205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348448</t>
+          <t>343253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>413479</t>
+          <t>409205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2233561</t>
+          <t>2233642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2345963</t>
+          <t>2354668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2233561</t>
+          <t>2233642</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2345963</t>
+          <t>2354668</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1176390</t>
+          <t>1167685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1288792</t>
+          <t>1288711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1176390</t>
+          <t>1167685</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1288792</t>
+          <t>1288711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>347554</t>
+          <t>344676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396955</t>
+          <t>396821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>347554</t>
+          <t>344676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>396955</t>
+          <t>396821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -3473,12 +3473,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268562</t>
+          <t>268696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>317963</t>
+          <t>320841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268562</t>
+          <t>268696</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>317963</t>
+          <t>320841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>639013</t>
+          <t>634732</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>700781</t>
+          <t>696045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>639013</t>
+          <t>634732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>700781</t>
+          <t>696045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325816</t>
+          <t>330552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387584</t>
+          <t>391865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325816</t>
+          <t>330552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>387584</t>
+          <t>391865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>480647</t>
+          <t>476889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>534238</t>
+          <t>532731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>480647</t>
+          <t>476889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>534238</t>
+          <t>532731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -3949,12 +3949,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>246566</t>
+          <t>248073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300157</t>
+          <t>303915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246566</t>
+          <t>248073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>300157</t>
+          <t>303915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>666322</t>
+          <t>664887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>725740</t>
+          <t>727823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>666322</t>
+          <t>664887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>725740</t>
+          <t>727823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308013</t>
+          <t>305930</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367431</t>
+          <t>368866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>308013</t>
+          <t>305930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367431</t>
+          <t>368866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -4347,12 +4347,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2183875</t>
+          <t>2178249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2297736</t>
+          <t>2294711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2183875</t>
+          <t>2178249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2297736</t>
+          <t>2294711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1208936</t>
+          <t>1211961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1328423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1208936</t>
+          <t>1211961</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1328423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -4751,32 +4751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>248548</t>
+          <t>264132</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285365</t>
+          <t>303457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4786,32 +4786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248548</t>
+          <t>264132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285365</t>
+          <t>303457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>55,31%</t>
         </is>
       </c>
     </row>
@@ -4829,32 +4829,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>238729</t>
+          <t>263198</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220797</t>
+          <t>245178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257614</t>
+          <t>284503</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4864,32 +4864,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>238729</t>
+          <t>263198</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220797</t>
+          <t>245178</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257614</t>
+          <t>284503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4907,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>506162</t>
+          <t>548635</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>506162</t>
+          <t>548635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>506162</t>
+          <t>548635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>506162</t>
+          <t>548635</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>506162</t>
+          <t>548635</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>506162</t>
+          <t>548635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4989,32 +4989,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>380965</t>
+          <t>423599</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>356534</t>
+          <t>397003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>404163</t>
+          <t>450627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5024,32 +5024,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>380965</t>
+          <t>423599</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>356534</t>
+          <t>397003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>404163</t>
+          <t>450627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -5067,32 +5067,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>347532</t>
+          <t>389879</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324334</t>
+          <t>362851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371963</t>
+          <t>416475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5102,32 +5102,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>347532</t>
+          <t>389879</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324334</t>
+          <t>362851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371963</t>
+          <t>416475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -5145,17 +5145,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>728497</t>
+          <t>813478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>728497</t>
+          <t>813478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>728497</t>
+          <t>813478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>728497</t>
+          <t>813478</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>728497</t>
+          <t>813478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>728497</t>
+          <t>813478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5227,32 +5227,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167640</t>
+          <t>344439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>508272</t>
+          <t>391448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5262,32 +5262,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167640</t>
+          <t>344439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>508272</t>
+          <t>391448</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -5305,32 +5305,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>370603</t>
+          <t>196292</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>216267</t>
+          <t>174407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>556899</t>
+          <t>221416</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5340,32 +5340,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>370603</t>
+          <t>196292</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>216267</t>
+          <t>174407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>556899</t>
+          <t>221416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -5383,17 +5383,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>724539</t>
+          <t>565855</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>724539</t>
+          <t>565855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>724539</t>
+          <t>565855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>724539</t>
+          <t>565855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>724539</t>
+          <t>565855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>724539</t>
+          <t>565855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5465,32 +5465,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531995</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>530715</t>
+          <t>503919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>634122</t>
+          <t>556917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5500,32 +5500,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531995</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>530715</t>
+          <t>503919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>634122</t>
+          <t>556917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -5543,32 +5543,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>279275</t>
+          <t>319919</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214108</t>
+          <t>294997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317515</t>
+          <t>347995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5578,32 +5578,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>279275</t>
+          <t>319919</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214108</t>
+          <t>294997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317515</t>
+          <t>347995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -5621,17 +5621,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>848230</t>
+          <t>851914</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>848230</t>
+          <t>851914</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>848230</t>
+          <t>851914</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>848230</t>
+          <t>851914</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>848230</t>
+          <t>851914</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>848230</t>
+          <t>851914</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5703,32 +5703,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1180025</t>
+          <t>1564073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1722853</t>
+          <t>1661715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5738,32 +5738,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1180025</t>
+          <t>1564073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1722853</t>
+          <t>1661715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -5781,32 +5781,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1236139</t>
+          <t>1169287</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1084575</t>
+          <t>1118167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1627403</t>
+          <t>1215809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1236139</t>
+          <t>1169287</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1084575</t>
+          <t>1118167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1627403</t>
+          <t>1215809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
